--- a/exports/PFC_full_report.xlsx
+++ b/exports/PFC_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q87"/>
+  <dimension ref="A1:U87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,22 +557,22 @@
         <v>4.19</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44582.38541666666</v>
+        <v>44582.55208333334</v>
       </c>
       <c r="H2" t="n">
-        <v>98.34999999999999</v>
+        <v>96.75</v>
       </c>
       <c r="I2" t="n">
         <v>98.20989663410352</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>11</v>
+        <v>11.16666666666667</v>
       </c>
       <c r="K2" t="n">
-        <v>-2.04</v>
+        <v>-3.64</v>
       </c>
       <c r="L2" t="n">
-        <v>2.39</v>
+        <v>4.38</v>
       </c>
       <c r="M2" t="n">
         <v>0.5</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>5.02</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44594.38541666666</v>
+        <v>44594.55208333334</v>
       </c>
       <c r="H3" t="n">
-        <v>98.25</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="I3" t="n">
         <v>98.33470435831855</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>11.83333333333333</v>
+        <v>12</v>
       </c>
       <c r="K3" t="n">
-        <v>-1.55</v>
+        <v>-1.71</v>
       </c>
       <c r="L3" t="n">
         <v>2.84</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,25 +695,25 @@
         <v>5.41</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44613.55208333334</v>
+        <v>44614.38541666666</v>
       </c>
       <c r="H4" t="n">
-        <v>95</v>
+        <v>92.7</v>
       </c>
       <c r="I4" t="n">
         <v>93.30848719611652</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>19</v>
+        <v>19.83333333333333</v>
       </c>
       <c r="K4" t="n">
-        <v>-3.46</v>
+        <v>-5.79</v>
       </c>
       <c r="L4" t="n">
         <v>6.4</v>
       </c>
       <c r="M4" t="n">
-        <v>1.06</v>
+        <v>1.47</v>
       </c>
       <c r="N4" t="n">
         <v>3.5</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>6.25</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44631.38541666666</v>
+        <v>44631.55208333334</v>
       </c>
       <c r="H5" t="n">
-        <v>89.55</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="I5" t="n">
         <v>90.02959667010441</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>17</v>
+        <v>17.16666666666667</v>
       </c>
       <c r="K5" t="n">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="L5" t="n">
         <v>3.24</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>5.97</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44673.55208333334</v>
+        <v>44676.38541666666</v>
       </c>
       <c r="H6" t="n">
-        <v>94.95</v>
+        <v>92.95</v>
       </c>
       <c r="I6" t="n">
         <v>93.53736691508946</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>42</v>
+        <v>44.83333333333334</v>
       </c>
       <c r="K6" t="n">
-        <v>5.38</v>
+        <v>3.16</v>
       </c>
       <c r="L6" t="n">
         <v>2.22</v>
@@ -783,7 +854,7 @@
         <v>0.63</v>
       </c>
       <c r="N6" t="n">
-        <v>2.07</v>
+        <v>2.32</v>
       </c>
       <c r="O6" t="n">
         <v>0.9</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>5.1</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44713.55208333334</v>
+        <v>44714.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>88.7</v>
+        <v>89.7</v>
       </c>
       <c r="I7" t="n">
         <v>89.33841316907625</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>37.16666666666666</v>
+        <v>38</v>
       </c>
       <c r="K7" t="n">
-        <v>4.57</v>
+        <v>3.5</v>
       </c>
       <c r="L7" t="n">
         <v>3.71</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -876,22 +971,22 @@
         <v>5.01</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44721.55208333334</v>
+        <v>44722.38541666666</v>
       </c>
       <c r="H8" t="n">
-        <v>86.95</v>
+        <v>85.84999999999999</v>
       </c>
       <c r="I8" t="n">
         <v>86.43149180186373</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K8" t="n">
-        <v>-3.07</v>
+        <v>-4.29</v>
       </c>
       <c r="L8" t="n">
-        <v>3.4</v>
+        <v>4.63</v>
       </c>
       <c r="M8" t="n">
         <v>1.13</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>4.63</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44736.55208333334</v>
+        <v>44739.38541666666</v>
       </c>
       <c r="H9" t="n">
-        <v>81.95</v>
+        <v>83.45</v>
       </c>
       <c r="I9" t="n">
         <v>82.81365881722154</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K9" t="n">
-        <v>4.54</v>
+        <v>2.8</v>
       </c>
       <c r="L9" t="n">
         <v>0.76</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S9" t="b">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>5.36</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44756.55208333334</v>
+        <v>44757.38541666666</v>
       </c>
       <c r="H10" t="n">
-        <v>86.45</v>
+        <v>85.2</v>
       </c>
       <c r="I10" t="n">
         <v>85.22806226580015</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>17.16666666666667</v>
+        <v>18</v>
       </c>
       <c r="K10" t="n">
-        <v>3.59</v>
+        <v>2.1</v>
       </c>
       <c r="L10" t="n">
         <v>1.74</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -1047,22 +1178,22 @@
         <v>4.68</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44761.38541666666</v>
+        <v>44761.55208333334</v>
       </c>
       <c r="H11" t="n">
-        <v>87.95</v>
+        <v>89.84999999999999</v>
       </c>
       <c r="I11" t="n">
         <v>88.8338681114009</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>4</v>
+        <v>4.166666666666667</v>
       </c>
       <c r="K11" t="n">
-        <v>-3.23</v>
+        <v>-5.46</v>
       </c>
       <c r="L11" t="n">
-        <v>4.34</v>
+        <v>5.75</v>
       </c>
       <c r="M11" t="n">
         <v>0.58</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S11" t="b">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>5.07</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44805.55208333334</v>
+        <v>44806.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>94.09999999999999</v>
+        <v>93.5</v>
       </c>
       <c r="I12" t="n">
         <v>93.66673619275343</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>44</v>
+        <v>44.83333333333334</v>
       </c>
       <c r="K12" t="n">
-        <v>4.73</v>
+        <v>4.06</v>
       </c>
       <c r="L12" t="n">
         <v>2.23</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>4.81</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44854.38541666666</v>
+        <v>44854.55208333334</v>
       </c>
       <c r="H13" t="n">
-        <v>83.90000000000001</v>
+        <v>84.5</v>
       </c>
       <c r="I13" t="n">
         <v>84.11010802021339</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>48</v>
+        <v>48.16666666666666</v>
       </c>
       <c r="K13" t="n">
-        <v>10.27</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="L13" t="n">
         <v>1.76</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>67</v>
+        <v>68</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>3.76</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44915.55208333334</v>
+        <v>44916.38541666666</v>
       </c>
       <c r="H14" t="n">
-        <v>113.2</v>
+        <v>111</v>
       </c>
       <c r="I14" t="n">
         <v>111.7933245067945</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>61</v>
+        <v>61.83333333333334</v>
       </c>
       <c r="K14" t="n">
-        <v>33.96</v>
+        <v>31.36</v>
       </c>
       <c r="L14" t="n">
         <v>0.83</v>
@@ -1239,7 +1406,7 @@
         <v>2.1</v>
       </c>
       <c r="N14" t="n">
-        <v>2.39</v>
+        <v>2.74</v>
       </c>
       <c r="O14" t="n">
         <v>1.38</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>82</v>
+        <v>83</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -1275,22 +1454,22 @@
         <v>7.27</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44924.55208333334</v>
+        <v>44925.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>110.5</v>
+        <v>113.15</v>
       </c>
       <c r="I15" t="n">
         <v>112.7871653315747</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K15" t="n">
-        <v>0.45</v>
+        <v>-1.94</v>
       </c>
       <c r="L15" t="n">
-        <v>3.02</v>
+        <v>3.15</v>
       </c>
       <c r="M15" t="n">
         <v>1.14</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,28 +1523,28 @@
         <v>6.54</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44950.55208333334</v>
+        <v>44951.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>119.8</v>
+        <v>115.15</v>
       </c>
       <c r="I16" t="n">
         <v>118.4225075150586</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>25.16666666666667</v>
+        <v>26</v>
       </c>
       <c r="K16" t="n">
-        <v>5.88</v>
+        <v>1.77</v>
       </c>
       <c r="L16" t="n">
         <v>2.25</v>
       </c>
       <c r="M16" t="n">
-        <v>0.16</v>
+        <v>0.25</v>
       </c>
       <c r="N16" t="n">
-        <v>2.59</v>
+        <v>4.09</v>
       </c>
       <c r="O16" t="n">
         <v>2.53</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>7.25</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>44966.38541666666</v>
+        <v>44966.55208333334</v>
       </c>
       <c r="H17" t="n">
-        <v>115.45</v>
+        <v>116.55</v>
       </c>
       <c r="I17" t="n">
         <v>116.4168059499743</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>15</v>
+        <v>15.16666666666667</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.26</v>
+        <v>-1.22</v>
       </c>
       <c r="L17" t="n">
         <v>3.78</v>
@@ -1419,7 +1622,19 @@
         <v>1</v>
       </c>
       <c r="Q17" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S17" t="b">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>6.62</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>44981.55208333334</v>
+        <v>44984.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>116</v>
+        <v>112.1</v>
       </c>
       <c r="I18" t="n">
         <v>113.5162811490122</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>15</v>
+        <v>17.83333333333333</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.47</v>
+        <v>-3.82</v>
       </c>
       <c r="L18" t="n">
         <v>6.18</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1503,22 +1730,22 @@
         <v>8.119999999999999</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>44986.55208333334</v>
+        <v>44987.38541666666</v>
       </c>
       <c r="H19" t="n">
-        <v>119.6</v>
+        <v>121.05</v>
       </c>
       <c r="I19" t="n">
         <v>120.8573092482091</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>2.166666666666667</v>
+        <v>3</v>
       </c>
       <c r="K19" t="n">
-        <v>-6.69</v>
+        <v>-7.98</v>
       </c>
       <c r="L19" t="n">
-        <v>7.09</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="M19" t="n">
         <v>0.5600000000000001</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S19" t="b">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>6.76</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45000.55208333334</v>
+        <v>45001.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>128.6</v>
+        <v>126.45</v>
       </c>
       <c r="I20" t="n">
         <v>127.1792792977787</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K20" t="n">
-        <v>6.24</v>
+        <v>4.46</v>
       </c>
       <c r="L20" t="n">
         <v>1.86</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S20" t="b">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>5.74</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45019.55208333334</v>
+        <v>45021.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>124.2</v>
+        <v>124.75</v>
       </c>
       <c r="I21" t="n">
         <v>124.5958851985558</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>18.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K21" t="n">
-        <v>1.78</v>
+        <v>1.34</v>
       </c>
       <c r="L21" t="n">
         <v>1.3</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>6.6</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45036.55208333334</v>
+        <v>45037.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>127.9</v>
+        <v>125.2</v>
       </c>
       <c r="I22" t="n">
         <v>126.8299537397935</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K22" t="n">
-        <v>2.53</v>
+        <v>0.36</v>
       </c>
       <c r="L22" t="n">
         <v>2</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S22" t="b">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,28 +2006,28 @@
         <v>7</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45043.55208333334</v>
+        <v>45044.38541666666</v>
       </c>
       <c r="H23" t="n">
-        <v>131.65</v>
+        <v>135.9</v>
       </c>
       <c r="I23" t="n">
         <v>132.1845855631087</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K23" t="n">
-        <v>-5.15</v>
+        <v>-8.550000000000001</v>
       </c>
       <c r="L23" t="n">
-        <v>6.35</v>
+        <v>8.83</v>
       </c>
       <c r="M23" t="n">
         <v>0.53</v>
       </c>
       <c r="N23" t="n">
-        <v>2.91</v>
+        <v>3.38</v>
       </c>
       <c r="O23" t="n">
         <v>-2.03</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,22 +2075,22 @@
         <v>6.7</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45057.38541666666</v>
+        <v>45057.55208333334</v>
       </c>
       <c r="H24" t="n">
-        <v>132.3</v>
+        <v>131.55</v>
       </c>
       <c r="I24" t="n">
         <v>132.1221577099899</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>13</v>
+        <v>13.16666666666667</v>
       </c>
       <c r="K24" t="n">
-        <v>-2.65</v>
+        <v>-3.2</v>
       </c>
       <c r="L24" t="n">
-        <v>3.31</v>
+        <v>3.68</v>
       </c>
       <c r="M24" t="n">
         <v>0.11</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S24" t="b">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1845,25 +2144,25 @@
         <v>6.2</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45072.55208333334</v>
+        <v>45075.38541666666</v>
       </c>
       <c r="H25" t="n">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="I25" t="n">
         <v>137.8807608130541</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>15</v>
+        <v>17.83333333333333</v>
       </c>
       <c r="K25" t="n">
-        <v>-3.38</v>
+        <v>-6.42</v>
       </c>
       <c r="L25" t="n">
-        <v>6.04</v>
+        <v>7.75</v>
       </c>
       <c r="M25" t="n">
-        <v>0.6899999999999999</v>
+        <v>2.24</v>
       </c>
       <c r="N25" t="n">
         <v>3.71</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>5.74</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45169.38541666666</v>
+        <v>45169.55208333334</v>
       </c>
       <c r="H26" t="n">
-        <v>215.1</v>
+        <v>206.6</v>
       </c>
       <c r="I26" t="n">
         <v>208.2039556228236</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>94</v>
+        <v>94.16666666666667</v>
       </c>
       <c r="K26" t="n">
-        <v>53.64</v>
+        <v>47.57</v>
       </c>
       <c r="L26" t="n">
         <v>1.64</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>133</v>
+        <v>134</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>3</v>
+      </c>
+      <c r="U26" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="27">
@@ -1959,22 +2282,22 @@
         <v>7.99</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45176.38541666666</v>
+        <v>45176.55208333334</v>
       </c>
       <c r="H27" t="n">
-        <v>214.35</v>
+        <v>218.3</v>
       </c>
       <c r="I27" t="n">
         <v>217.2025492614568</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>6.833333333333333</v>
+        <v>7</v>
       </c>
       <c r="K27" t="n">
-        <v>-3.75</v>
+        <v>-5.66</v>
       </c>
       <c r="L27" t="n">
-        <v>4.36</v>
+        <v>5.71</v>
       </c>
       <c r="M27" t="n">
         <v>0.58</v>
@@ -1989,7 +2312,19 @@
         <v>1</v>
       </c>
       <c r="Q27" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S27" t="b">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>7.61</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45181.55208333334</v>
+        <v>45182.38541666666</v>
       </c>
       <c r="H28" t="n">
-        <v>226.4</v>
+        <v>223.1</v>
       </c>
       <c r="I28" t="n">
         <v>225.9896562429422</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>5</v>
+        <v>5.833333333333333</v>
       </c>
       <c r="K28" t="n">
-        <v>3.71</v>
+        <v>2.2</v>
       </c>
       <c r="L28" t="n">
         <v>2.5</v>
@@ -2046,7 +2381,19 @@
         <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S28" t="b">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,28 +2420,28 @@
         <v>11.42</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45195.55208333334</v>
+        <v>45196.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>235.45</v>
+        <v>251.75</v>
       </c>
       <c r="I29" t="n">
         <v>242.1081218567416</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K29" t="n">
-        <v>-5.54</v>
+        <v>-12.84</v>
       </c>
       <c r="L29" t="n">
-        <v>8.09</v>
+        <v>13.9</v>
       </c>
       <c r="M29" t="n">
         <v>1.12</v>
       </c>
       <c r="N29" t="n">
-        <v>3.45</v>
+        <v>5.92</v>
       </c>
       <c r="O29" t="n">
         <v>-1.46</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S29" t="b">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2130,22 +2489,22 @@
         <v>10.48</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45222.55208333334</v>
+        <v>45224.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>242.5</v>
+        <v>234.6</v>
       </c>
       <c r="I30" t="n">
         <v>238.5980795724469</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>26.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K30" t="n">
-        <v>-3.67</v>
+        <v>-6.81</v>
       </c>
       <c r="L30" t="n">
-        <v>6.47</v>
+        <v>6.81</v>
       </c>
       <c r="M30" t="n">
         <v>1.32</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,28 +2558,28 @@
         <v>10.6</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45231.55208333334</v>
+        <v>45232.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>242.55</v>
+        <v>258.3</v>
       </c>
       <c r="I31" t="n">
         <v>248.4905117288782</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K31" t="n">
-        <v>-3.39</v>
+        <v>-10.1</v>
       </c>
       <c r="L31" t="n">
-        <v>6.22</v>
+        <v>10.53</v>
       </c>
       <c r="M31" t="n">
         <v>1.52</v>
       </c>
       <c r="N31" t="n">
-        <v>3.14</v>
+        <v>5.94</v>
       </c>
       <c r="O31" t="n">
         <v>-2.02</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>10.76</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45280.38541666666</v>
+        <v>45280.55208333334</v>
       </c>
       <c r="H32" t="n">
-        <v>403.2</v>
+        <v>379.15</v>
       </c>
       <c r="I32" t="n">
         <v>393.6423480540626</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>48</v>
+        <v>48.16666666666666</v>
       </c>
       <c r="K32" t="n">
-        <v>56.1</v>
+        <v>46.79</v>
       </c>
       <c r="L32" t="n">
         <v>5.15</v>
@@ -2274,7 +2657,19 @@
         <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>12.15</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45310.38541666666</v>
+        <v>45310.55208333334</v>
       </c>
       <c r="H33" t="n">
-        <v>409.65</v>
+        <v>412.4</v>
       </c>
       <c r="I33" t="n">
         <v>412.1327100239494</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>29.83333333333333</v>
+        <v>30</v>
       </c>
       <c r="K33" t="n">
-        <v>-8.039999999999999</v>
+        <v>-8.77</v>
       </c>
       <c r="L33" t="n">
         <v>9.18</v>
@@ -2331,7 +2726,19 @@
         <v>1</v>
       </c>
       <c r="Q33" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,28 +2765,28 @@
         <v>8.16</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45330.55208333334</v>
+        <v>45331.38541666666</v>
       </c>
       <c r="H34" t="n">
-        <v>467.15</v>
+        <v>420.6</v>
       </c>
       <c r="I34" t="n">
         <v>436.7138015567463</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>20</v>
+        <v>20.83333333333333</v>
       </c>
       <c r="K34" t="n">
-        <v>13.28</v>
+        <v>1.99</v>
       </c>
       <c r="L34" t="n">
         <v>7.25</v>
       </c>
       <c r="M34" t="n">
-        <v>0.7</v>
+        <v>0.89</v>
       </c>
       <c r="N34" t="n">
-        <v>4.58</v>
+        <v>8.06</v>
       </c>
       <c r="O34" t="n">
         <v>4.67</v>
@@ -2388,7 +2795,19 @@
         <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>14.89</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45357.38541666666</v>
+        <v>45357.55208333334</v>
       </c>
       <c r="H35" t="n">
-        <v>421.5</v>
+        <v>423.45</v>
       </c>
       <c r="I35" t="n">
         <v>421.6620011885511</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>26</v>
+        <v>26.16666666666667</v>
       </c>
       <c r="K35" t="n">
-        <v>-0.21</v>
+        <v>-0.68</v>
       </c>
       <c r="L35" t="n">
         <v>10.08</v>
@@ -2445,7 +2864,19 @@
         <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,28 +2903,28 @@
         <v>6.82</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45363.55208333334</v>
+        <v>45364.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>427.9</v>
+        <v>404</v>
       </c>
       <c r="I36" t="n">
         <v>405.8841329996942</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>6</v>
+        <v>6.833333333333333</v>
       </c>
       <c r="K36" t="n">
-        <v>1.05</v>
+        <v>-4.59</v>
       </c>
       <c r="L36" t="n">
-        <v>0.7</v>
+        <v>6.05</v>
       </c>
       <c r="M36" t="n">
         <v>0.02</v>
       </c>
       <c r="N36" t="n">
-        <v>0.68</v>
+        <v>7.22</v>
       </c>
       <c r="O36" t="n">
         <v>1.35</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S36" t="b">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>10.44</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45379.55208333334</v>
+        <v>45383.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>391.55</v>
+        <v>400.8</v>
       </c>
       <c r="I37" t="n">
         <v>396.171294409455</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K37" t="n">
-        <v>3.08</v>
+        <v>0.79</v>
       </c>
       <c r="L37" t="n">
         <v>6.42</v>
@@ -2559,7 +3002,19 @@
         <v>1</v>
       </c>
       <c r="Q37" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,28 +3041,28 @@
         <v>8.140000000000001</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45415.55208333334</v>
+        <v>45418.38541666666</v>
       </c>
       <c r="H38" t="n">
-        <v>481.6</v>
+        <v>439.1</v>
       </c>
       <c r="I38" t="n">
         <v>443.3249901969597</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>32.16666666666666</v>
+        <v>35</v>
       </c>
       <c r="K38" t="n">
-        <v>20.16</v>
+        <v>9.56</v>
       </c>
       <c r="L38" t="n">
         <v>3.94</v>
       </c>
       <c r="M38" t="n">
-        <v>2.31</v>
+        <v>5.21</v>
       </c>
       <c r="N38" t="n">
-        <v>2.84</v>
+        <v>9.26</v>
       </c>
       <c r="O38" t="n">
         <v>2.43</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="39">
@@ -2643,22 +3110,22 @@
         <v>11.44</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45428.55208333334</v>
+        <v>45429.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>454</v>
+        <v>464.5</v>
       </c>
       <c r="I39" t="n">
         <v>456.4964140565174</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>11</v>
       </c>
       <c r="K39" t="n">
-        <v>-3.39</v>
+        <v>-5.78</v>
       </c>
       <c r="L39" t="n">
-        <v>4.5</v>
+        <v>6.04</v>
       </c>
       <c r="M39" t="n">
         <v>1.37</v>
@@ -2673,7 +3140,19 @@
         <v>1</v>
       </c>
       <c r="Q39" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S39" t="b">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -2700,28 +3179,28 @@
         <v>9.32</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45446.55208333334</v>
+        <v>45447.38541666666</v>
       </c>
       <c r="H40" t="n">
-        <v>558.55</v>
+        <v>442.65</v>
       </c>
       <c r="I40" t="n">
         <v>498.7575839959376</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>17.16666666666667</v>
+        <v>18</v>
       </c>
       <c r="K40" t="n">
-        <v>20.25</v>
+        <v>-4.7</v>
       </c>
       <c r="L40" t="n">
-        <v>2.26</v>
+        <v>10.42</v>
       </c>
       <c r="M40" t="n">
-        <v>0.31</v>
+        <v>2.44</v>
       </c>
       <c r="N40" t="n">
-        <v>1.98</v>
+        <v>22.12</v>
       </c>
       <c r="O40" t="n">
         <v>3.15</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>29.48</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45475.55208333334</v>
+        <v>45476.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>502.6</v>
+        <v>528.5</v>
       </c>
       <c r="I41" t="n">
         <v>508.4893199530494</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>28.16666666666667</v>
+        <v>29</v>
       </c>
       <c r="K41" t="n">
-        <v>-13.54</v>
+        <v>-19.39</v>
       </c>
       <c r="L41" t="n">
         <v>23.1</v>
@@ -2787,7 +3278,19 @@
         <v>1</v>
       </c>
       <c r="Q41" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>7.99</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45492.38541666666</v>
+        <v>45492.55208333334</v>
       </c>
       <c r="H42" t="n">
-        <v>539.95</v>
+        <v>533.2</v>
       </c>
       <c r="I42" t="n">
         <v>535.8105471069541</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>16</v>
+        <v>16.16666666666667</v>
       </c>
       <c r="K42" t="n">
-        <v>2.17</v>
+        <v>0.89</v>
       </c>
       <c r="L42" t="n">
         <v>3.41</v>
@@ -2844,7 +3347,19 @@
         <v>1</v>
       </c>
       <c r="Q42" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S42" t="b">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>8.27</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45530.55208333334</v>
+        <v>45531.38541666666</v>
       </c>
       <c r="H43" t="n">
-        <v>514.85</v>
+        <v>530</v>
       </c>
       <c r="I43" t="n">
         <v>521.3330065949726</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>38</v>
+        <v>38.83333333333334</v>
       </c>
       <c r="K43" t="n">
-        <v>3.44</v>
+        <v>0.6</v>
       </c>
       <c r="L43" t="n">
         <v>5.5</v>
@@ -2892,7 +3407,7 @@
         <v>3.74</v>
       </c>
       <c r="N43" t="n">
-        <v>3.85</v>
+        <v>3.94</v>
       </c>
       <c r="O43" t="n">
         <v>-2.59</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>6.89</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45541.55208333334</v>
+        <v>45544.38541666666</v>
       </c>
       <c r="H44" t="n">
-        <v>545.45</v>
+        <v>515.8</v>
       </c>
       <c r="I44" t="n">
         <v>530.0245697035787</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K44" t="n">
-        <v>2.92</v>
+        <v>-2.68</v>
       </c>
       <c r="L44" t="n">
         <v>3.35</v>
@@ -2949,7 +3476,7 @@
         <v>1.88</v>
       </c>
       <c r="N44" t="n">
-        <v>2.34</v>
+        <v>3.73</v>
       </c>
       <c r="O44" t="n">
         <v>3.94</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>9.859999999999999</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45580.38541666666</v>
+        <v>45580.55208333334</v>
       </c>
       <c r="H45" t="n">
-        <v>476.1</v>
+        <v>477.8</v>
       </c>
       <c r="I45" t="n">
         <v>476.3386674189769</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>36</v>
+        <v>36.16666666666666</v>
       </c>
       <c r="K45" t="n">
-        <v>7.7</v>
+        <v>7.37</v>
       </c>
       <c r="L45" t="n">
         <v>5.55</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -3042,28 +3593,28 @@
         <v>6.27</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45586.55208333334</v>
+        <v>45587.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>462.65</v>
+        <v>449.6</v>
       </c>
       <c r="I46" t="n">
         <v>453.6221945881058</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>6</v>
+        <v>6.833333333333333</v>
       </c>
       <c r="K46" t="n">
-        <v>-3.17</v>
+        <v>-5.9</v>
       </c>
       <c r="L46" t="n">
-        <v>4.29</v>
+        <v>6.3</v>
       </c>
       <c r="M46" t="n">
         <v>0.19</v>
       </c>
       <c r="N46" t="n">
-        <v>2.16</v>
+        <v>3.96</v>
       </c>
       <c r="O46" t="n">
         <v>0.8</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S46" t="b">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>1</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -3099,22 +3662,22 @@
         <v>8</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45594.38541666666</v>
+        <v>45594.55208333334</v>
       </c>
       <c r="H47" t="n">
-        <v>455.7</v>
+        <v>473.4</v>
       </c>
       <c r="I47" t="n">
         <v>469.0325830026479</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>7</v>
+        <v>7.166666666666667</v>
       </c>
       <c r="K47" t="n">
-        <v>-1.36</v>
+        <v>-5.29</v>
       </c>
       <c r="L47" t="n">
-        <v>3.47</v>
+        <v>5.43</v>
       </c>
       <c r="M47" t="n">
         <v>0.55</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S47" t="b">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>1</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>10.31</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45643.55208333334</v>
+        <v>45644.38541666666</v>
       </c>
       <c r="H48" t="n">
-        <v>497.5</v>
+        <v>487.25</v>
       </c>
       <c r="I48" t="n">
         <v>492.4474499203891</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>49</v>
+        <v>49.83333333333334</v>
       </c>
       <c r="K48" t="n">
-        <v>5.09</v>
+        <v>2.93</v>
       </c>
       <c r="L48" t="n">
         <v>8.58</v>
@@ -3186,7 +3761,19 @@
         <v>1</v>
       </c>
       <c r="Q48" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>3</v>
+      </c>
+      <c r="U48" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>5.92</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45659.55208333334</v>
+        <v>45660.38541666666</v>
       </c>
       <c r="H49" t="n">
-        <v>459.45</v>
+        <v>473.35</v>
       </c>
       <c r="I49" t="n">
         <v>471.1538215595631</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K49" t="n">
-        <v>5.71</v>
+        <v>2.85</v>
       </c>
       <c r="L49" t="n">
         <v>2.29</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,22 +3869,22 @@
         <v>6.88</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45664.55208333334</v>
+        <v>45665.38541666666</v>
       </c>
       <c r="H50" t="n">
-        <v>445.9</v>
+        <v>431.7</v>
       </c>
       <c r="I50" t="n">
         <v>442.310583485667</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>5</v>
       </c>
       <c r="K50" t="n">
-        <v>-5.8</v>
+        <v>-8.800000000000001</v>
       </c>
       <c r="L50" t="n">
-        <v>6.5</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="M50" t="n">
         <v>0.05</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S50" t="b">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>1</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>8.81</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45671.55208333334</v>
+        <v>45672.38541666666</v>
       </c>
       <c r="H51" t="n">
-        <v>418.8</v>
+        <v>428.85</v>
       </c>
       <c r="I51" t="n">
         <v>423.9692269649933</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K51" t="n">
-        <v>2.99</v>
+        <v>0.66</v>
       </c>
       <c r="L51" t="n">
         <v>3.75</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S51" t="b">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>1</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,22 +4007,22 @@
         <v>8.949999999999999</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45681.38541666666</v>
+        <v>45681.55208333334</v>
       </c>
       <c r="H52" t="n">
-        <v>411.8</v>
+        <v>407.95</v>
       </c>
       <c r="I52" t="n">
         <v>410.8404006242458</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>9</v>
+        <v>9.166666666666666</v>
       </c>
       <c r="K52" t="n">
-        <v>-3.98</v>
+        <v>-4.87</v>
       </c>
       <c r="L52" t="n">
-        <v>4.15</v>
+        <v>5.07</v>
       </c>
       <c r="M52" t="n">
         <v>0.5600000000000001</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S52" t="b">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>1</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -3441,22 +4076,22 @@
         <v>7.07</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45687.55208333334</v>
+        <v>45688.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>414.5</v>
+        <v>421.3</v>
       </c>
       <c r="I53" t="n">
         <v>418.3820143766914</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>6</v>
+        <v>6.833333333333333</v>
       </c>
       <c r="K53" t="n">
-        <v>-1.61</v>
+        <v>-3.27</v>
       </c>
       <c r="L53" t="n">
-        <v>2.21</v>
+        <v>3.68</v>
       </c>
       <c r="M53" t="n">
         <v>2.75</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,25 +4145,25 @@
         <v>9.33</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45689.55208333334</v>
+        <v>45691.38541666666</v>
       </c>
       <c r="H54" t="n">
-        <v>403.8</v>
+        <v>382.05</v>
       </c>
       <c r="I54" t="n">
         <v>388.1963971785858</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>1.166666666666667</v>
+        <v>3</v>
       </c>
       <c r="K54" t="n">
-        <v>-4.15</v>
+        <v>-9.32</v>
       </c>
       <c r="L54" t="n">
-        <v>4.64</v>
+        <v>10.23</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="N54" t="n">
         <v>4.76</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S54" t="b">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>1</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>12.65</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45720.55208333334</v>
+        <v>45721.38541666666</v>
       </c>
       <c r="H55" t="n">
-        <v>383.4</v>
+        <v>395.6</v>
       </c>
       <c r="I55" t="n">
         <v>391.0712668160711</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>29.16666666666667</v>
+        <v>30</v>
       </c>
       <c r="K55" t="n">
-        <v>-0.35</v>
+        <v>-3.55</v>
       </c>
       <c r="L55" t="n">
         <v>9.880000000000001</v>
@@ -3585,7 +4244,19 @@
         <v>1</v>
       </c>
       <c r="Q55" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,25 +4283,25 @@
         <v>9.18</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45751.55208333334</v>
+        <v>45754.38541666666</v>
       </c>
       <c r="H56" t="n">
-        <v>408.4</v>
+        <v>387</v>
       </c>
       <c r="I56" t="n">
         <v>400.6301527611806</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>30.16666666666667</v>
+        <v>33</v>
       </c>
       <c r="K56" t="n">
-        <v>3.24</v>
+        <v>-2.17</v>
       </c>
       <c r="L56" t="n">
-        <v>3.56</v>
+        <v>5.99</v>
       </c>
       <c r="M56" t="n">
-        <v>1.42</v>
+        <v>8.42</v>
       </c>
       <c r="N56" t="n">
         <v>3.1</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3669,28 +4352,28 @@
         <v>8.390000000000001</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45758.55208333334</v>
+        <v>45762.38541666666</v>
       </c>
       <c r="H57" t="n">
-        <v>401.85</v>
+        <v>420.85</v>
       </c>
       <c r="I57" t="n">
         <v>419.4765024631064</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K57" t="n">
-        <v>-3.84</v>
+        <v>-8.75</v>
       </c>
       <c r="L57" t="n">
-        <v>6.8</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="M57" t="n">
-        <v>1.31</v>
+        <v>2.33</v>
       </c>
       <c r="N57" t="n">
-        <v>1.53</v>
+        <v>6.23</v>
       </c>
       <c r="O57" t="n">
         <v>-3.02</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S57" t="b">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>1</v>
+      </c>
+      <c r="U57" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -3726,22 +4421,22 @@
         <v>9.57</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45776.55208333334</v>
+        <v>45777.38541666666</v>
       </c>
       <c r="H58" t="n">
-        <v>413.15</v>
+        <v>410.65</v>
       </c>
       <c r="I58" t="n">
         <v>411.7926765209717</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K58" t="n">
-        <v>-1.83</v>
+        <v>-2.42</v>
       </c>
       <c r="L58" t="n">
-        <v>3.12</v>
+        <v>3.14</v>
       </c>
       <c r="M58" t="n">
         <v>0.3</v>
@@ -3756,7 +4451,19 @@
         <v>1</v>
       </c>
       <c r="Q58" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3783,19 +4490,19 @@
         <v>7.26</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45789.38541666666</v>
+        <v>45789.55208333334</v>
       </c>
       <c r="H59" t="n">
-        <v>408.25</v>
+        <v>414.65</v>
       </c>
       <c r="I59" t="n">
         <v>412.4435032233694</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>12</v>
+        <v>12.16666666666667</v>
       </c>
       <c r="K59" t="n">
-        <v>0.58</v>
+        <v>-0.97</v>
       </c>
       <c r="L59" t="n">
         <v>1.42</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S59" t="b">
+        <v>0</v>
+      </c>
+      <c r="T59" t="n">
+        <v>1</v>
+      </c>
+      <c r="U59" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -3840,25 +4559,25 @@
         <v>8.15</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45820.55208333334</v>
+        <v>45821.38541666666</v>
       </c>
       <c r="H60" t="n">
-        <v>415.1</v>
+        <v>404.15</v>
       </c>
       <c r="I60" t="n">
         <v>414.4817510389731</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>31</v>
+        <v>31.83333333333333</v>
       </c>
       <c r="K60" t="n">
-        <v>0.11</v>
+        <v>-2.53</v>
       </c>
       <c r="L60" t="n">
-        <v>3.16</v>
+        <v>3.29</v>
       </c>
       <c r="M60" t="n">
-        <v>0.64</v>
+        <v>3.4</v>
       </c>
       <c r="N60" t="n">
         <v>3</v>
@@ -3870,7 +4589,19 @@
         <v>1</v>
       </c>
       <c r="Q60" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>2</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -3897,22 +4628,22 @@
         <v>5.73</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45831.55208333334</v>
+        <v>45832.38541666666</v>
       </c>
       <c r="H61" t="n">
-        <v>410.75</v>
+        <v>416.8</v>
       </c>
       <c r="I61" t="n">
         <v>411.8295452664812</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>11</v>
       </c>
       <c r="K61" t="n">
-        <v>-1.63</v>
+        <v>-3.13</v>
       </c>
       <c r="L61" t="n">
-        <v>2.68</v>
+        <v>4.12</v>
       </c>
       <c r="M61" t="n">
         <v>2.31</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S61" t="b">
+        <v>0</v>
+      </c>
+      <c r="T61" t="n">
+        <v>1</v>
+      </c>
+      <c r="U61" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>5.62</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45863.55208333334</v>
+        <v>45866.38541666666</v>
       </c>
       <c r="H62" t="n">
-        <v>415.55</v>
+        <v>410.35</v>
       </c>
       <c r="I62" t="n">
         <v>414.0094297134663</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>31.16666666666667</v>
+        <v>34</v>
       </c>
       <c r="K62" t="n">
-        <v>-0.3</v>
+        <v>-1.55</v>
       </c>
       <c r="L62" t="n">
         <v>1.69</v>
@@ -3975,7 +4718,7 @@
         <v>0.36</v>
       </c>
       <c r="N62" t="n">
-        <v>1.58</v>
+        <v>2.55</v>
       </c>
       <c r="O62" t="n">
         <v>0.67</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>2</v>
+      </c>
+      <c r="U62" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -4011,22 +4766,22 @@
         <v>4.84</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>45880.55208333334</v>
+        <v>45881.38541666666</v>
       </c>
       <c r="H63" t="n">
-        <v>419.3</v>
+        <v>421.75</v>
       </c>
       <c r="I63" t="n">
         <v>421.5538315749598</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K63" t="n">
-        <v>-2.18</v>
+        <v>-2.78</v>
       </c>
       <c r="L63" t="n">
-        <v>2.33</v>
+        <v>3.55</v>
       </c>
       <c r="M63" t="n">
         <v>0.36</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -4068,22 +4835,22 @@
         <v>4.83</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>45890.38541666666</v>
+        <v>45890.55208333334</v>
       </c>
       <c r="H64" t="n">
-        <v>404.4</v>
+        <v>399.8</v>
       </c>
       <c r="I64" t="n">
         <v>401.3706080959635</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>9</v>
+        <v>9.166666666666666</v>
       </c>
       <c r="K64" t="n">
-        <v>-4.11</v>
+        <v>-5.2</v>
       </c>
       <c r="L64" t="n">
-        <v>4.45</v>
+        <v>5.32</v>
       </c>
       <c r="M64" t="n">
         <v>0.16</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S64" t="b">
+        <v>0</v>
+      </c>
+      <c r="T64" t="n">
+        <v>1</v>
+      </c>
+      <c r="U64" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -4125,19 +4904,19 @@
         <v>4.78</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>45905.55208333334</v>
+        <v>45908.38541666666</v>
       </c>
       <c r="H65" t="n">
-        <v>394.75</v>
+        <v>398.2</v>
       </c>
       <c r="I65" t="n">
         <v>395.3269083250979</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>15</v>
+        <v>17.83333333333333</v>
       </c>
       <c r="K65" t="n">
-        <v>1.26</v>
+        <v>0.4</v>
       </c>
       <c r="L65" t="n">
         <v>1.18</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>2</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -4182,19 +4973,19 @@
         <v>4.19</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>45925.55208333334</v>
+        <v>45926.38541666666</v>
       </c>
       <c r="H66" t="n">
-        <v>404</v>
+        <v>398.45</v>
       </c>
       <c r="I66" t="n">
         <v>401.7158838031344</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>17.16666666666667</v>
+        <v>18</v>
       </c>
       <c r="K66" t="n">
-        <v>1.46</v>
+        <v>0.06</v>
       </c>
       <c r="L66" t="n">
         <v>1.43</v>
@@ -4203,7 +4994,7 @@
         <v>0.34</v>
       </c>
       <c r="N66" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="O66" t="n">
         <v>0.22</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S66" t="b">
+        <v>0</v>
+      </c>
+      <c r="T66" t="n">
+        <v>1</v>
+      </c>
+      <c r="U66" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -4239,22 +5042,22 @@
         <v>4.43</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>45930.38541666666</v>
+        <v>45930.55208333334</v>
       </c>
       <c r="H67" t="n">
-        <v>407.4</v>
+        <v>411.1</v>
       </c>
       <c r="I67" t="n">
         <v>410.6990288457785</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>4</v>
+        <v>4.166666666666667</v>
       </c>
       <c r="K67" t="n">
-        <v>-2.25</v>
+        <v>-3.17</v>
       </c>
       <c r="L67" t="n">
-        <v>2.5</v>
+        <v>3.17</v>
       </c>
       <c r="M67" t="n">
         <v>0.29</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S67" t="b">
+        <v>0</v>
+      </c>
+      <c r="T67" t="n">
+        <v>1</v>
+      </c>
+      <c r="U67" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -4296,22 +5111,22 @@
         <v>4</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>45938.38541666666</v>
+        <v>45938.55208333334</v>
       </c>
       <c r="H68" t="n">
-        <v>400.8</v>
+        <v>399.5</v>
       </c>
       <c r="I68" t="n">
         <v>400.0875299568563</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>7.833333333333333</v>
+        <v>8</v>
       </c>
       <c r="K68" t="n">
-        <v>-2.51</v>
+        <v>-2.82</v>
       </c>
       <c r="L68" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="M68" t="n">
         <v>0.64</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S68" t="b">
+        <v>0</v>
+      </c>
+      <c r="T68" t="n">
+        <v>1</v>
+      </c>
+      <c r="U68" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -4353,22 +5180,22 @@
         <v>4.26</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>45959.38541666666</v>
+        <v>45959.55208333334</v>
       </c>
       <c r="H69" t="n">
-        <v>404.7</v>
+        <v>410.5</v>
       </c>
       <c r="I69" t="n">
         <v>406.886897705192</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>20.83333333333333</v>
+        <v>21</v>
       </c>
       <c r="K69" t="n">
-        <v>-1.3</v>
+        <v>-2.75</v>
       </c>
       <c r="L69" t="n">
-        <v>2.35</v>
+        <v>2.88</v>
       </c>
       <c r="M69" t="n">
         <v>1</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>2</v>
+      </c>
+      <c r="U69" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -4410,28 +5249,28 @@
         <v>4.88</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>45965.55208333334</v>
+        <v>45967.38541666666</v>
       </c>
       <c r="H70" t="n">
-        <v>396.5</v>
+        <v>389.65</v>
       </c>
       <c r="I70" t="n">
         <v>390.4804121716551</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>6</v>
+        <v>7.833333333333333</v>
       </c>
       <c r="K70" t="n">
-        <v>-3.41</v>
+        <v>-5.08</v>
       </c>
       <c r="L70" t="n">
-        <v>3.63</v>
+        <v>5.44</v>
       </c>
       <c r="M70" t="n">
         <v>0.25</v>
       </c>
       <c r="N70" t="n">
-        <v>1.73</v>
+        <v>2.27</v>
       </c>
       <c r="O70" t="n">
         <v>3.95</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S70" t="b">
+        <v>0</v>
+      </c>
+      <c r="T70" t="n">
+        <v>1</v>
+      </c>
+      <c r="U70" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -4467,19 +5318,19 @@
         <v>5.22</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>46013.55208333334</v>
+        <v>46014.38541666666</v>
       </c>
       <c r="H71" t="n">
-        <v>343</v>
+        <v>354.95</v>
       </c>
       <c r="I71" t="n">
         <v>346.84427846813</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>46.16666666666666</v>
+        <v>47</v>
       </c>
       <c r="K71" t="n">
-        <v>11.97</v>
+        <v>8.91</v>
       </c>
       <c r="L71" t="n">
         <v>2.13</v>
@@ -4488,7 +5339,7 @@
         <v>0.6</v>
       </c>
       <c r="N71" t="n">
-        <v>1.33</v>
+        <v>3.62</v>
       </c>
       <c r="O71" t="n">
         <v>-2.27</v>
@@ -4497,7 +5348,19 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>2</v>
+      </c>
+      <c r="U71" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="72">
@@ -4524,19 +5387,19 @@
         <v>5.83</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>46031.38541666666</v>
+        <v>46031.55208333334</v>
       </c>
       <c r="H72" t="n">
-        <v>361.85</v>
+        <v>359.4</v>
       </c>
       <c r="I72" t="n">
         <v>360.8821980329753</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>17</v>
+        <v>17.16666666666667</v>
       </c>
       <c r="K72" t="n">
-        <v>1.94</v>
+        <v>1.25</v>
       </c>
       <c r="L72" t="n">
         <v>3.52</v>
@@ -4554,7 +5417,19 @@
         <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S72" t="b">
+        <v>1</v>
+      </c>
+      <c r="T72" t="n">
+        <v>2</v>
+      </c>
+      <c r="U72" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="73">
@@ -4581,19 +5456,19 @@
         <v>5.44</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>46049.55208333334</v>
+        <v>46050.38541666666</v>
       </c>
       <c r="H73" t="n">
-        <v>363</v>
+        <v>377.25</v>
       </c>
       <c r="I73" t="n">
         <v>376.4605322541134</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>18</v>
+        <v>18.83333333333333</v>
       </c>
       <c r="K73" t="n">
-        <v>-1</v>
+        <v>-4.97</v>
       </c>
       <c r="L73" t="n">
         <v>5.5</v>
@@ -4602,7 +5477,7 @@
         <v>0.67</v>
       </c>
       <c r="N73" t="n">
-        <v>3.67</v>
+        <v>5.79</v>
       </c>
       <c r="O73" t="n">
         <v>-1.24</v>
@@ -4611,7 +5486,19 @@
         <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R73" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S73" t="b">
+        <v>1</v>
+      </c>
+      <c r="T73" t="n">
+        <v>2</v>
+      </c>
+      <c r="U73" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -4638,19 +5525,19 @@
         <v>7.88</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>46083.55208333334</v>
+        <v>46085.38541666666</v>
       </c>
       <c r="H74" t="n">
-        <v>405.6</v>
+        <v>396.9</v>
       </c>
       <c r="I74" t="n">
         <v>399.3125663561903</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>33.16666666666666</v>
+        <v>35</v>
       </c>
       <c r="K74" t="n">
-        <v>7.51</v>
+        <v>5.21</v>
       </c>
       <c r="L74" t="n">
         <v>4</v>
@@ -4659,7 +5546,7 @@
         <v>2.98</v>
       </c>
       <c r="N74" t="n">
-        <v>2.89</v>
+        <v>3.51</v>
       </c>
       <c r="O74" t="n">
         <v>5.79</v>
@@ -4668,7 +5555,19 @@
         <v>1</v>
       </c>
       <c r="Q74" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R74" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S74" t="b">
+        <v>1</v>
+      </c>
+      <c r="T74" t="n">
+        <v>2</v>
+      </c>
+      <c r="U74" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="75">
@@ -4695,22 +5594,22 @@
         <v>6.65</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>46098.55208333334</v>
+        <v>46099.38541666666</v>
       </c>
       <c r="H75" t="n">
-        <v>417.25</v>
+        <v>430</v>
       </c>
       <c r="I75" t="n">
         <v>420.2979008560648</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K75" t="n">
-        <v>-5.13</v>
+        <v>-8.34</v>
       </c>
       <c r="L75" t="n">
-        <v>7.12</v>
+        <v>9.59</v>
       </c>
       <c r="M75" t="n">
         <v>1.7</v>
@@ -4725,7 +5624,19 @@
         <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R75" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S75" t="b">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -4752,25 +5663,25 @@
         <v>8.49</v>
       </c>
       <c r="G76" s="1" t="n">
-        <v>46101.55208333334</v>
+        <v>46104.38541666666</v>
       </c>
       <c r="H76" t="n">
-        <v>411.9</v>
+        <v>393.5</v>
       </c>
       <c r="I76" t="n">
         <v>399.2083847606519</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>2.166666666666667</v>
+        <v>5</v>
       </c>
       <c r="K76" t="n">
-        <v>-4.21</v>
+        <v>-8.49</v>
       </c>
       <c r="L76" t="n">
-        <v>4.86</v>
+        <v>10.14</v>
       </c>
       <c r="M76" t="n">
-        <v>2.13</v>
+        <v>2.17</v>
       </c>
       <c r="N76" t="n">
         <v>4.23</v>
@@ -4782,7 +5693,19 @@
         <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R76" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S76" t="b">
+        <v>0</v>
+      </c>
+      <c r="T76" t="n">
+        <v>1</v>
+      </c>
+      <c r="U76" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="77">
@@ -4809,25 +5732,25 @@
         <v>9.57</v>
       </c>
       <c r="G77" s="1" t="n">
-        <v>46119.55208333334</v>
+        <v>46120.38541666666</v>
       </c>
       <c r="H77" t="n">
-        <v>405.8</v>
+        <v>416.9</v>
       </c>
       <c r="I77" t="n">
         <v>408.7787523644363</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K77" t="n">
-        <v>-3.13</v>
+        <v>-5.95</v>
       </c>
       <c r="L77" t="n">
-        <v>4.1</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="M77" t="n">
-        <v>3.52</v>
+        <v>4.24</v>
       </c>
       <c r="N77" t="n">
         <v>4.74</v>
@@ -4839,7 +5762,19 @@
         <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R77" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S77" t="b">
+        <v>1</v>
+      </c>
+      <c r="T77" t="n">
+        <v>2</v>
+      </c>
+      <c r="U77" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="78">
@@ -4866,19 +5801,19 @@
         <v>6.93</v>
       </c>
       <c r="G78" s="1" t="n">
-        <v>46141.55208333334</v>
+        <v>46142.38541666666</v>
       </c>
       <c r="H78" t="n">
-        <v>464</v>
+        <v>450.05</v>
       </c>
       <c r="I78" t="n">
         <v>456.5556557953055</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K78" t="n">
-        <v>11.3</v>
+        <v>7.95</v>
       </c>
       <c r="L78" t="n">
         <v>0.83</v>
@@ -4887,7 +5822,7 @@
         <v>2.98</v>
       </c>
       <c r="N78" t="n">
-        <v>2.52</v>
+        <v>3.09</v>
       </c>
       <c r="O78" t="n">
         <v>3.1</v>
@@ -4896,7 +5831,19 @@
         <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R78" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S78" t="b">
+        <v>1</v>
+      </c>
+      <c r="T78" t="n">
+        <v>2</v>
+      </c>
+      <c r="U78" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="79">
@@ -4923,19 +5870,19 @@
         <v>7.73</v>
       </c>
       <c r="G79" s="1" t="n">
-        <v>46178.55208333334</v>
+        <v>46181.38541666666</v>
       </c>
       <c r="H79" t="n">
-        <v>431.5</v>
+        <v>433.95</v>
       </c>
       <c r="I79" t="n">
         <v>432.7678996344488</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>36.16666666666666</v>
+        <v>39</v>
       </c>
       <c r="K79" t="n">
-        <v>4.12</v>
+        <v>3.58</v>
       </c>
       <c r="L79" t="n">
         <v>3.86</v>
@@ -4953,7 +5900,19 @@
         <v>0</v>
       </c>
       <c r="Q79" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R79" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S79" t="b">
+        <v>1</v>
+      </c>
+      <c r="T79" t="n">
+        <v>2</v>
+      </c>
+      <c r="U79" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="80">
@@ -4980,22 +5939,22 @@
         <v>6.23</v>
       </c>
       <c r="G80" s="1" t="n">
-        <v>46184.38541666666</v>
+        <v>46184.55208333334</v>
       </c>
       <c r="H80" t="n">
-        <v>415</v>
+        <v>414.3</v>
       </c>
       <c r="I80" t="n">
         <v>414.8161867699196</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="K80" t="n">
-        <v>-4.37</v>
+        <v>-4.53</v>
       </c>
       <c r="L80" t="n">
-        <v>4.42</v>
+        <v>4.94</v>
       </c>
       <c r="M80" t="n">
         <v>1.23</v>
@@ -5010,7 +5969,19 @@
         <v>0</v>
       </c>
       <c r="Q80" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R80" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S80" t="b">
+        <v>0</v>
+      </c>
+      <c r="T80" t="n">
+        <v>1</v>
+      </c>
+      <c r="U80" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="81">
@@ -5037,28 +6008,28 @@
         <v>5.42</v>
       </c>
       <c r="G81" s="1" t="n">
-        <v>46192.55208333334</v>
+        <v>46195.38541666666</v>
       </c>
       <c r="H81" t="n">
-        <v>430.5</v>
+        <v>439.95</v>
       </c>
       <c r="I81" t="n">
         <v>436.7757248447286</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>8</v>
+        <v>10.83333333333333</v>
       </c>
       <c r="K81" t="n">
-        <v>-3.91</v>
+        <v>-6.19</v>
       </c>
       <c r="L81" t="n">
-        <v>5.39</v>
+        <v>7.36</v>
       </c>
       <c r="M81" t="n">
         <v>1.31</v>
       </c>
       <c r="N81" t="n">
-        <v>1.62</v>
+        <v>2.42</v>
       </c>
       <c r="O81" t="n">
         <v>-3.87</v>
@@ -5067,7 +6038,19 @@
         <v>0</v>
       </c>
       <c r="Q81" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R81" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S81" t="b">
+        <v>0</v>
+      </c>
+      <c r="T81" t="n">
+        <v>1</v>
+      </c>
+      <c r="U81" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -5094,28 +6077,28 @@
         <v>5.77</v>
       </c>
       <c r="G82" s="1" t="n">
-        <v>46209.55208333334</v>
+        <v>46210.38541666666</v>
       </c>
       <c r="H82" t="n">
-        <v>421.55</v>
+        <v>416.45</v>
       </c>
       <c r="I82" t="n">
         <v>419.3527276890513</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K82" t="n">
-        <v>-4.18</v>
+        <v>-5.34</v>
       </c>
       <c r="L82" t="n">
-        <v>4.53</v>
+        <v>5.64</v>
       </c>
       <c r="M82" t="n">
         <v>0.61</v>
       </c>
       <c r="N82" t="n">
-        <v>2.18</v>
+        <v>2.43</v>
       </c>
       <c r="O82" t="n">
         <v>2.42</v>
@@ -5124,7 +6107,19 @@
         <v>0</v>
       </c>
       <c r="Q82" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R82" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S82" t="b">
+        <v>1</v>
+      </c>
+      <c r="T82" t="n">
+        <v>2</v>
+      </c>
+      <c r="U82" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="83">
@@ -5151,22 +6146,22 @@
         <v>4.8</v>
       </c>
       <c r="G83" s="1" t="n">
-        <v>46230.55208333334</v>
+        <v>46231.38541666666</v>
       </c>
       <c r="H83" t="n">
-        <v>418.25</v>
+        <v>420.4</v>
       </c>
       <c r="I83" t="n">
         <v>418.9960900092029</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K83" t="n">
-        <v>-0.43</v>
+        <v>-0.95</v>
       </c>
       <c r="L83" t="n">
-        <v>1.44</v>
+        <v>1.69</v>
       </c>
       <c r="M83" t="n">
         <v>0.92</v>
@@ -5181,7 +6176,19 @@
         <v>0</v>
       </c>
       <c r="Q83" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R83" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S83" t="b">
+        <v>0</v>
+      </c>
+      <c r="T83" t="n">
+        <v>1</v>
+      </c>
+      <c r="U83" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -5208,28 +6215,28 @@
         <v>4.06</v>
       </c>
       <c r="G84" s="1" t="n">
-        <v>46241.55208333334</v>
+        <v>46244.38541666666</v>
       </c>
       <c r="H84" t="n">
-        <v>419</v>
+        <v>385.25</v>
       </c>
       <c r="I84" t="n">
         <v>410.2669451810202</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K84" t="n">
-        <v>-0.33</v>
+        <v>-8.359999999999999</v>
       </c>
       <c r="L84" t="n">
-        <v>1.77</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="M84" t="n">
-        <v>0.48</v>
+        <v>1.65</v>
       </c>
       <c r="N84" t="n">
-        <v>1.72</v>
+        <v>8.09</v>
       </c>
       <c r="O84" t="n">
         <v>0.37</v>
@@ -5238,7 +6245,19 @@
         <v>0</v>
       </c>
       <c r="Q84" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R84" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S84" t="b">
+        <v>0</v>
+      </c>
+      <c r="T84" t="n">
+        <v>1</v>
+      </c>
+      <c r="U84" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -5265,19 +6284,19 @@
         <v>9.73</v>
       </c>
       <c r="G85" s="1" t="n">
-        <v>46304.55208333334</v>
+        <v>46307.38541666666</v>
       </c>
       <c r="H85" t="n">
-        <v>328.7</v>
+        <v>332.65</v>
       </c>
       <c r="I85" t="n">
         <v>331.8678350000337</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>60.16666666666666</v>
+        <v>63</v>
       </c>
       <c r="K85" t="n">
-        <v>14.68</v>
+        <v>13.65</v>
       </c>
       <c r="L85" t="n">
         <v>7.63</v>
@@ -5295,7 +6314,19 @@
         <v>1</v>
       </c>
       <c r="Q85" t="n">
-        <v>86</v>
+        <v>87</v>
+      </c>
+      <c r="R85" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S85" t="b">
+        <v>1</v>
+      </c>
+      <c r="T85" t="n">
+        <v>3</v>
+      </c>
+      <c r="U85" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="86">
@@ -5322,22 +6353,22 @@
         <v>5.06</v>
       </c>
       <c r="G86" s="1" t="n">
-        <v>46314.55208333334</v>
+        <v>46316.38541666666</v>
       </c>
       <c r="H86" t="n">
-        <v>331.4</v>
+        <v>325.05</v>
       </c>
       <c r="I86" t="n">
         <v>330.2939019765429</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>9</v>
       </c>
       <c r="K86" t="n">
-        <v>-0.38</v>
+        <v>-2.28</v>
       </c>
       <c r="L86" t="n">
-        <v>1.37</v>
+        <v>2.43</v>
       </c>
       <c r="M86" t="n">
         <v>0.43</v>
@@ -5352,7 +6383,19 @@
         <v>0</v>
       </c>
       <c r="Q86" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R86" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S86" t="b">
+        <v>0</v>
+      </c>
+      <c r="T86" t="n">
+        <v>1</v>
+      </c>
+      <c r="U86" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="87">
@@ -5403,6 +6446,12 @@
       <c r="Q87" t="n">
         <v>10</v>
       </c>
+      <c r="R87" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S87" t="inlineStr"/>
+      <c r="T87" t="inlineStr"/>
+      <c r="U87" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7505,7 +8554,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>19.4</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="6">
@@ -7515,7 +8564,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7">
@@ -7525,7 +8574,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>94</v>
+        <v>94.2</v>
       </c>
     </row>
     <row r="8">
@@ -7535,7 +8584,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -7545,7 +8594,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>26.2</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10">
@@ -7555,7 +8604,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>40.4</v>
+        <v>42.5</v>
       </c>
     </row>
     <row r="11">
@@ -7595,7 +8644,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.38</v>
+        <v>-0.51</v>
       </c>
     </row>
     <row r="15">
@@ -7605,7 +8654,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4.84</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="16">
@@ -7615,7 +8664,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.14</v>
+        <v>-2.33</v>
       </c>
     </row>
     <row r="17">
@@ -7625,7 +8674,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>56.1</v>
+        <v>47.57</v>
       </c>
     </row>
     <row r="18">
@@ -7635,7 +8684,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>45.9</v>
+        <v>37.6</v>
       </c>
     </row>
     <row r="19">
@@ -7645,7 +8694,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4.16</v>
+        <v>5.19</v>
       </c>
     </row>
     <row r="20">
@@ -7655,7 +8704,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.56</v>
+        <v>4.38</v>
       </c>
     </row>
     <row r="21">
@@ -7675,7 +8724,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>24</v>
+        <v>40</v>
       </c>
     </row>
     <row r="23">
@@ -7685,7 +8734,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24">
@@ -7695,7 +8744,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.17</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="25">
@@ -7705,7 +8754,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4.32</v>
+        <v>8.42</v>
       </c>
     </row>
     <row r="26">
@@ -7715,7 +8764,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.42</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="27">
@@ -7725,7 +8774,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>7.84</v>
+        <v>22.12</v>
       </c>
     </row>
     <row r="28">
@@ -7735,7 +8784,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
     </row>
     <row r="29">
